--- a/basedatos_partidas/salida/descompuestos/CT-12-04-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-04-050.xlsx
@@ -591,10 +591,10 @@
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>23.42</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="16">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>39.75</v>
+        <v>39.35</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>40.15</v>
+        <v>39.74</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-12-04-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-04-050.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -643,10 +643,10 @@
         <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>23.02</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="16">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>39.35</v>
+        <v>41.58</v>
       </c>
       <c r="H24" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>39.74</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-12-04-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-04-050.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 12 Instalaciones sanitarias</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Aparatos sanitarios y grifería</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
